--- a/Tests/resultTB.xlsx
+++ b/Tests/resultTB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Programming\python\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6295C3-86A4-424A-A5E1-243A1B551FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0508423B-03B8-47E8-B8EA-B6447DCE3A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="5100" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18015" yWindow="4035" windowWidth="28800" windowHeight="13980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -1091,10 +1091,11 @@
   <dimension ref="A1:F228"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="43.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="16.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
